--- a/Stuecklisten/Elektrobox_Stückliste.xlsx
+++ b/Stuecklisten/Elektrobox_Stückliste.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HTL\SPL\CandyMaschine_Project\CandyMachine_Watermelon\Stuecklisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B48E8A-B290-4329-8BA6-5E860E87743D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB39AC3-512C-4640-AC2A-2771B9A78ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" xr2:uid="{9DA56051-2903-42FB-B064-034924F5A5D2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Anzahl</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>Artikelnummer</t>
-  </si>
-  <si>
-    <t>Spannungsverteiler</t>
   </si>
   <si>
     <t>H-Brücke</t>
@@ -115,6 +112,18 @@
       <t>DEBO DUPON 4PIN</t>
     </r>
   </si>
+  <si>
+    <t>Spannungsverteiler (Kabel)</t>
+  </si>
+  <si>
+    <t>https://at.rs-online.com/web/p/idc-steckverbinder/6257252</t>
+  </si>
+  <si>
+    <t>Spannungsverteiler (Befestigung)</t>
+  </si>
+  <si>
+    <t>304-04-769</t>
+  </si>
 </sst>
 </file>
 
@@ -122,7 +131,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-407]_-;\-* #,##0.00\ [$€-407]_-;_-* &quot;-&quot;??\ [$€-407]_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="#,##0.00\ [$€-1];[Red]\-#,##0.00\ [$€-1]"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ [$€-1];[Red]\-#,##0.00\ [$€-1]"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -244,7 +253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -280,12 +289,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -310,13 +320,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>808080</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>26400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>831120</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>139080</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
@@ -719,12 +729,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C109D0D-11F1-44AC-92C4-98F0FB4A2F8E}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.6640625" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -750,13 +760,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="4">
         <v>19.8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" s="10">
         <v>7630049203969</v>
@@ -767,91 +777,108 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="6">
         <v>5.29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C4" s="6">
-        <v>24.19</v>
+        <v>5.26</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>10</v>
+        <v>23</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="5">
-        <v>8.56</v>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="6">
+        <v>24.19</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5">
+        <v>8.56</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="9">
         <v>2050005748030</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
+    <row r="8" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
         <v>1</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="15">
+        <v>0.43</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>20</v>
-      </c>
-      <c r="C7" s="15">
-        <v>0.43</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{00BC4F0C-D697-4CE4-8278-4A347B796AA4}"/>
-    <hyperlink ref="B6" r:id="rId2" display="https://www.conrad.at/de/p/tru-components-yst-1102a-drucktaster-12-v-dc-0-05-a-1-x-aus-ein-tastend-l-x-b-6-mm-x-6-mm-1-st-1569018.html?insert=UP&amp;utm_source=google-shopping-de&amp;utm_medium=search&amp;utm_campaign=shopping-online-de&amp;utm_content=shopping-ad_cpc&amp;WT.srch=1&amp;ef_id=CjwKCAiAvaLLBhBFEiwAYCNTf908VSnv0s-MmemZj0iv06QLJpiNhpOEHccYiJTgeAskNOWtXxIFdhoCrUYQAvD_BwE:G:s&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=Shopping_AT_2025&amp;utm_id=22317741252&amp;gad_source=1&amp;gad_campaignid=22317741252&amp;gclid=CjwKCAiAvaLLBhBFEiwAYCNTf908VSnv0s-MmemZj0iv06QLJpiNhpOEHccYiJTgeAskNOWtXxIFdhoCrUYQAvD_BwE" xr:uid="{0FB896CA-FEB2-49BE-B56E-71A9F627FA4E}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{14FF0BA6-C637-4C91-B94F-D9D5AC390328}"/>
+    <hyperlink ref="B7" r:id="rId2" display="https://www.conrad.at/de/p/tru-components-yst-1102a-drucktaster-12-v-dc-0-05-a-1-x-aus-ein-tastend-l-x-b-6-mm-x-6-mm-1-st-1569018.html?insert=UP&amp;utm_source=google-shopping-de&amp;utm_medium=search&amp;utm_campaign=shopping-online-de&amp;utm_content=shopping-ad_cpc&amp;WT.srch=1&amp;ef_id=CjwKCAiAvaLLBhBFEiwAYCNTf908VSnv0s-MmemZj0iv06QLJpiNhpOEHccYiJTgeAskNOWtXxIFdhoCrUYQAvD_BwE:G:s&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=Shopping_AT_2025&amp;utm_id=22317741252&amp;gad_source=1&amp;gad_campaignid=22317741252&amp;gclid=CjwKCAiAvaLLBhBFEiwAYCNTf908VSnv0s-MmemZj0iv06QLJpiNhpOEHccYiJTgeAskNOWtXxIFdhoCrUYQAvD_BwE" xr:uid="{0FB896CA-FEB2-49BE-B56E-71A9F627FA4E}"/>
+    <hyperlink ref="B6" r:id="rId3" xr:uid="{14FF0BA6-C637-4C91-B94F-D9D5AC390328}"/>
     <hyperlink ref="B2" r:id="rId4" xr:uid="{AA090009-CE3F-4B35-82FF-326E27EDA40A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
